--- a/backend/fuel-market-information/fuel-market-information.xlsx
+++ b/backend/fuel-market-information/fuel-market-information.xlsx
@@ -6,7 +6,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="E-Cooking" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Electricity" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="LPG" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Carbon" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
@@ -500,7 +500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O5"/>
+  <dimension ref="A1:N5"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1">
@@ -521,60 +521,55 @@
       </c>
       <c r="D1" s="2" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E1" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F1" s="2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="H1" s="2" t="inlineStr">
         <is>
-          <t>2027</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="I1" s="2" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>2029</t>
         </is>
       </c>
       <c r="J1" s="2" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>2030</t>
         </is>
       </c>
       <c r="K1" s="2" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>2031</t>
         </is>
       </c>
       <c r="L1" s="2" t="inlineStr">
         <is>
-          <t>2031</t>
+          <t>2032</t>
         </is>
       </c>
       <c r="M1" s="2" t="inlineStr">
         <is>
-          <t>2032</t>
+          <t>2033</t>
         </is>
       </c>
       <c r="N1" s="2" t="inlineStr">
-        <is>
-          <t>2033</t>
-        </is>
-      </c>
-      <c r="O1" s="2" t="inlineStr">
         <is>
           <t>2034</t>
         </is>
@@ -627,9 +622,6 @@
       <c r="N2" t="n">
         <v>0</v>
       </c>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -678,9 +670,6 @@
       <c r="N3" t="n">
         <v>0</v>
       </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -729,9 +718,6 @@
       <c r="N4" t="n">
         <v>0</v>
       </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -778,9 +764,6 @@
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -795,7 +778,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O7"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="31.6328125" customWidth="1" min="1" max="1"/>
@@ -819,60 +802,55 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>2027</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>2029</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>2030</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>2031</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>2031</t>
+          <t>2032</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>2032</t>
+          <t>2033</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>2033</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>2034</t>
         </is>
@@ -925,9 +903,6 @@
       <c r="N2" t="n">
         <v>0</v>
       </c>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -976,9 +951,6 @@
       <c r="N3" t="n">
         <v>0</v>
       </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1027,9 +999,6 @@
       <c r="N4" t="n">
         <v>0</v>
       </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1078,9 +1047,6 @@
       <c r="N5" t="n">
         <v>0</v>
       </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1129,9 +1095,6 @@
       <c r="N6" t="n">
         <v>0</v>
       </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1178,9 +1141,6 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1195,7 +1155,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O5"/>
+  <dimension ref="A1:N5"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="31.6328125" customWidth="1" min="1" max="1"/>
@@ -1219,60 +1179,55 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>2027</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>2029</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>2030</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>2031</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>2031</t>
+          <t>2032</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>2032</t>
+          <t>2033</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>2033</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>2034</t>
         </is>
@@ -1325,9 +1280,6 @@
       <c r="N2" t="n">
         <v>0</v>
       </c>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1376,9 +1328,6 @@
       <c r="N3" t="n">
         <v>0</v>
       </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1427,9 +1376,6 @@
       <c r="N4" t="n">
         <v>0</v>
       </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1496,11 +1442,6 @@
         </is>
       </c>
       <c r="N5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
         <is>
           <t>-</t>
         </is>

--- a/backend/fuel-market-information/fuel-market-information.xlsx
+++ b/backend/fuel-market-information/fuel-market-information.xlsx
@@ -778,7 +778,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N7"/>
+  <dimension ref="A1:N11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="31.6328125" customWidth="1" min="1" max="1"/>
@@ -1141,6 +1141,198 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>% EBITDA Margin - CleanStep</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>OPEX subsidies - CleanStep</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>% EBITDA Margin - BAU</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>OPEX subsidies - BAU</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
         <v>0</v>
       </c>
     </row>

--- a/backend/fuel-market-information/fuel-market-information.xlsx
+++ b/backend/fuel-market-information/fuel-market-information.xlsx
@@ -778,7 +778,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N7"/>
+  <dimension ref="A1:N5"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="31.6328125" customWidth="1" min="1" max="1"/>
@@ -1045,102 +1045,6 @@
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>% EBITDA Margin - Aligned</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>OPEX subsidies - Aligned</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
         <v>0</v>
       </c>
     </row>

--- a/backend/fuel-market-information/fuel-market-information.xlsx
+++ b/backend/fuel-market-information/fuel-market-information.xlsx
@@ -500,7 +500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH5"/>
+  <dimension ref="A1:N5"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1">
@@ -521,157 +521,57 @@
       </c>
       <c r="D1" s="2" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E1" s="2" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F1" s="2" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="H1" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="I1" s="2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2029</t>
         </is>
       </c>
       <c r="J1" s="2" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2030</t>
         </is>
       </c>
       <c r="K1" s="2" t="inlineStr">
         <is>
-          <t>2027</t>
+          <t>2031</t>
         </is>
       </c>
       <c r="L1" s="2" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>2032</t>
         </is>
       </c>
       <c r="M1" s="2" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>2033</t>
         </is>
       </c>
       <c r="N1" s="2" t="inlineStr">
         <is>
-          <t>2030</t>
-        </is>
-      </c>
-      <c r="O1" s="2" t="inlineStr">
-        <is>
-          <t>2031</t>
-        </is>
-      </c>
-      <c r="P1" s="2" t="inlineStr">
-        <is>
-          <t>2032</t>
-        </is>
-      </c>
-      <c r="Q1" s="2" t="inlineStr">
-        <is>
-          <t>2033</t>
-        </is>
-      </c>
-      <c r="R1" s="2" t="inlineStr">
-        <is>
           <t>2034</t>
-        </is>
-      </c>
-      <c r="S1" s="2" t="inlineStr">
-        <is>
-          <t>2035</t>
-        </is>
-      </c>
-      <c r="T1" s="2" t="inlineStr">
-        <is>
-          <t>2036</t>
-        </is>
-      </c>
-      <c r="U1" s="2" t="inlineStr">
-        <is>
-          <t>2037</t>
-        </is>
-      </c>
-      <c r="V1" s="2" t="inlineStr">
-        <is>
-          <t>2038</t>
-        </is>
-      </c>
-      <c r="W1" s="2" t="inlineStr">
-        <is>
-          <t>2039</t>
-        </is>
-      </c>
-      <c r="X1" s="2" t="inlineStr">
-        <is>
-          <t>2040</t>
-        </is>
-      </c>
-      <c r="Y1" s="2" t="inlineStr">
-        <is>
-          <t>2041</t>
-        </is>
-      </c>
-      <c r="Z1" s="2" t="inlineStr">
-        <is>
-          <t>2042</t>
-        </is>
-      </c>
-      <c r="AA1" s="2" t="inlineStr">
-        <is>
-          <t>2043</t>
-        </is>
-      </c>
-      <c r="AB1" s="2" t="inlineStr">
-        <is>
-          <t>2044</t>
-        </is>
-      </c>
-      <c r="AC1" s="2" t="inlineStr">
-        <is>
-          <t>2045</t>
-        </is>
-      </c>
-      <c r="AD1" s="2" t="inlineStr">
-        <is>
-          <t>2046</t>
-        </is>
-      </c>
-      <c r="AE1" s="2" t="inlineStr">
-        <is>
-          <t>2047</t>
-        </is>
-      </c>
-      <c r="AF1" s="2" t="inlineStr">
-        <is>
-          <t>2048</t>
-        </is>
-      </c>
-      <c r="AG1" s="2" t="inlineStr">
-        <is>
-          <t>2049</t>
-        </is>
-      </c>
-      <c r="AH1" s="2" t="inlineStr">
-        <is>
-          <t>2050</t>
         </is>
       </c>
     </row>
@@ -722,66 +622,6 @@
       <c r="N2" t="n">
         <v>0</v>
       </c>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V2" t="n">
-        <v>0</v>
-      </c>
-      <c r="W2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -830,66 +670,6 @@
       <c r="N3" t="n">
         <v>0</v>
       </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -938,66 +718,6 @@
       <c r="N4" t="n">
         <v>0</v>
       </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1044,66 +764,6 @@
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1118,7 +778,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH5"/>
+  <dimension ref="A1:N5"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="31.6328125" customWidth="1" min="1" max="1"/>
@@ -1142,157 +802,57 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2029</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2030</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>2027</t>
+          <t>2031</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>2032</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>2033</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>2030</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>2031</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>2032</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>2033</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
           <t>2034</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>2035</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>2036</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>2037</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>2038</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>2039</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>2040</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>2041</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>2042</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>2043</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>2044</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>2045</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>2046</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>2047</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>2048</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>2049</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>2050</t>
         </is>
       </c>
     </row>
@@ -1343,66 +903,6 @@
       <c r="N2" t="n">
         <v>0</v>
       </c>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V2" t="n">
-        <v>0</v>
-      </c>
-      <c r="W2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1451,66 +951,6 @@
       <c r="N3" t="n">
         <v>0</v>
       </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1559,66 +999,6 @@
       <c r="N4" t="n">
         <v>0</v>
       </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1665,66 +1045,6 @@
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1739,7 +1059,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH5"/>
+  <dimension ref="A1:N5"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="31.6328125" customWidth="1" min="1" max="1"/>
@@ -1763,157 +1083,57 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2029</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2030</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>2027</t>
+          <t>2031</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>2032</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>2033</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>2030</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>2031</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>2032</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>2033</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
           <t>2034</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>2035</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>2036</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>2037</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>2038</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>2039</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>2040</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>2041</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>2042</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>2043</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>2044</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>2045</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>2046</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>2047</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>2048</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>2049</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>2050</t>
         </is>
       </c>
     </row>
@@ -1964,66 +1184,6 @@
       <c r="N2" t="n">
         <v>0</v>
       </c>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V2" t="n">
-        <v>0</v>
-      </c>
-      <c r="W2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2072,66 +1232,6 @@
       <c r="N3" t="n">
         <v>0</v>
       </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2180,66 +1280,6 @@
       <c r="N4" t="n">
         <v>0</v>
       </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2306,106 +1346,6 @@
         </is>
       </c>
       <c r="N5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
         <is>
           <t>-</t>
         </is>

--- a/backend/fuel-market-information/fuel-market-information.xlsx
+++ b/backend/fuel-market-information/fuel-market-information.xlsx
@@ -790,7 +790,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N7"/>
+  <dimension ref="A1:N9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1151,6 +1151,102 @@
       </c>
       <c r="N7" t="n">
         <v>20</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>% EBITDA Margin - CleanStep</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>OPEX subsidies - CleanStep</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/backend/fuel-market-information/fuel-market-information.xlsx
+++ b/backend/fuel-market-information/fuel-market-information.xlsx
@@ -1,9 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr codeName="ThisWorkbook"/>
+  <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Electricity" sheetId="1" state="visible" r:id="rId1"/>
@@ -11,37 +12,19 @@
     <sheet name="Carbon" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1" iterate="1"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="2">
     <font>
-      <name val="Aptos Narrow"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <b val="1"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <b val="1"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <sz val="8"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -56,42 +39,12 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -104,22 +57,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -192,7 +139,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -202,44 +149,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="0E2841"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E8E8E8"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="156082"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="E97132"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="196B24"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="0F9ED5"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="A02B93"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="4EA72E"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="467886"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="96607D"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -266,32 +213,14 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -318,24 +247,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -347,162 +258,166 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="35000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="80000">
               <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
-            <a:schemeClr val="phClr"/>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="40000">
               <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
@@ -516,72 +431,72 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Inputs</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Units</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Baseline</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>2027</t>
         </is>
       </c>
-      <c r="H1" s="3" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>2028</t>
         </is>
       </c>
-      <c r="I1" s="3" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>2029</t>
         </is>
       </c>
-      <c r="J1" s="3" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>2030</t>
         </is>
       </c>
-      <c r="K1" s="3" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>2031</t>
         </is>
       </c>
-      <c r="L1" s="3" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>2032</t>
         </is>
       </c>
-      <c r="M1" s="3" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>2033</t>
         </is>
       </c>
-      <c r="N1" s="3" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>2034</t>
         </is>
@@ -794,72 +709,72 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Inputs</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Units</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Baseline</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>2027</t>
         </is>
       </c>
-      <c r="H1" s="3" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>2028</t>
         </is>
       </c>
-      <c r="I1" s="3" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>2029</t>
         </is>
       </c>
-      <c r="J1" s="3" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>2030</t>
         </is>
       </c>
-      <c r="K1" s="3" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>2031</t>
         </is>
       </c>
-      <c r="L1" s="3" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>2032</t>
         </is>
       </c>
-      <c r="M1" s="3" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>2033</t>
         </is>
       </c>
-      <c r="N1" s="3" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>2034</t>
         </is>
@@ -1264,72 +1179,72 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Inputs</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Units</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Baseline</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>2027</t>
         </is>
       </c>
-      <c r="H1" s="3" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>2028</t>
         </is>
       </c>
-      <c r="I1" s="3" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>2029</t>
         </is>
       </c>
-      <c r="J1" s="3" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>2030</t>
         </is>
       </c>
-      <c r="K1" s="3" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>2031</t>
         </is>
       </c>
-      <c r="L1" s="3" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>2032</t>
         </is>
       </c>
-      <c r="M1" s="3" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>2033</t>
         </is>
       </c>
-      <c r="N1" s="3" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>2034</t>
         </is>
